--- a/public/employee_upload_sample1.xlsx
+++ b/public/employee_upload_sample1.xlsx
@@ -1145,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BG1"/>
+  <dimension ref="A1:BJ1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="28" max="28" width="18.4285714285714" customWidth="1"/>
@@ -1333,6 +1333,21 @@
       <c r="BG1" t="s">
         <v>58</v>
       </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Sub-Department 1</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Sub-Department 2</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Sub-Department 3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
